--- a/data/trans_dic/P25A$medico-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25A$medico-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, el consejo médico</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, el consejo médico (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,43; 40,53</t>
+          <t>15,6; 40,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,22; 21,63</t>
+          <t>6,48; 21,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 10,71</t>
+          <t>1,25; 10,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,49</t>
+          <t>0,0; 15,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,83</t>
+          <t>0,0; 12,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,46; 28,86</t>
+          <t>10,66; 29,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,51; 17,2</t>
+          <t>5,4; 16,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 8,76</t>
+          <t>1,52; 8,33</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,11; 38,35</t>
+          <t>21,73; 39,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,96; 29,71</t>
+          <t>14,81; 30,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,77; 35,67</t>
+          <t>14,27; 35,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,61</t>
+          <t>0,0; 27,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,9</t>
+          <t>1,58; 14,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,07</t>
+          <t>0,0; 22,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,15; 33,35</t>
+          <t>18,13; 32,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,97; 22,06</t>
+          <t>10,86; 22,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,08; 27,71</t>
+          <t>12,2; 27,41</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 25,19</t>
+          <t>7,25; 24,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,39; 36,89</t>
+          <t>17,3; 36,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,34; 28,84</t>
+          <t>10,44; 28,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,84</t>
+          <t>0,0; 39,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 23,25</t>
+          <t>2,67; 22,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,1</t>
+          <t>0,0; 17,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,87; 23,56</t>
+          <t>8,29; 23,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,09; 29,73</t>
+          <t>14,52; 28,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,9; 20,94</t>
+          <t>8,31; 21,6</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,74; 34,28</t>
+          <t>15,42; 33,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 15,15</t>
+          <t>3,83; 14,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,87; 18,99</t>
+          <t>5,9; 18,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,9</t>
+          <t>0,0; 14,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,74</t>
+          <t>0,0; 12,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,34</t>
+          <t>0,0; 11,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,58; 24,13</t>
+          <t>10,85; 24,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 11,92</t>
+          <t>2,81; 10,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 13,9</t>
+          <t>4,26; 13,34</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,13; 29,92</t>
+          <t>7,79; 29,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 23,49</t>
+          <t>2,0; 23,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 28,88</t>
+          <t>2,64; 31,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,37</t>
+          <t>0,0; 25,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 30,0</t>
+          <t>3,47; 27,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,04</t>
+          <t>0,0; 34,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,14; 22,14</t>
+          <t>6,29; 21,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 20,33</t>
+          <t>4,03; 20,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,0; 23,37</t>
+          <t>3,58; 22,73</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,21; 40,64</t>
+          <t>18,89; 41,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,49; 31,5</t>
+          <t>12,91; 31,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,2; 30,57</t>
+          <t>7,87; 29,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,48; 40,07</t>
+          <t>5,41; 40,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,73</t>
+          <t>0,0; 22,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,69; 37,76</t>
+          <t>17,03; 36,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,86; 25,52</t>
+          <t>11,66; 26,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,48; 21,2</t>
+          <t>5,68; 22,13</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,69; 33,75</t>
+          <t>16,65; 34,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,34; 33,06</t>
+          <t>18,82; 33,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28,23; 46,7</t>
+          <t>29,43; 47,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,66</t>
+          <t>0,0; 26,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,25; 22,69</t>
+          <t>7,86; 23,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,29; 30,19</t>
+          <t>11,83; 28,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,41; 28,43</t>
+          <t>14,37; 27,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,48; 27,23</t>
+          <t>16,48; 27,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>24,31; 37,81</t>
+          <t>24,58; 37,65</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>29,43; 46,27</t>
+          <t>29,73; 45,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,79; 34,28</t>
+          <t>16,79; 33,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,43; 23,35</t>
+          <t>9,51; 23,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,71; 21,83</t>
+          <t>5,6; 21,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,12; 22,86</t>
+          <t>6,26; 23,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,39; 18,25</t>
+          <t>3,42; 18,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,11; 35,11</t>
+          <t>22,61; 35,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,84; 27,23</t>
+          <t>14,76; 26,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,95; 18,75</t>
+          <t>8,16; 19,27</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>23,46; 30,66</t>
+          <t>23,79; 30,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,9; 22,57</t>
+          <t>16,95; 22,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16,13; 22,83</t>
+          <t>16,24; 23,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,34; 13,31</t>
+          <t>5,14; 12,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,3; 12,19</t>
+          <t>6,25; 12,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,33; 12,48</t>
+          <t>6,17; 12,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,99; 24,54</t>
+          <t>19,02; 24,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,96; 18,48</t>
+          <t>14,13; 18,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,39; 18,38</t>
+          <t>13,44; 18,12</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, el consejo médico</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, el consejo médico (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7168; 18825</t>
+          <t>7247; 18796</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5044; 17544</t>
+          <t>5252; 17432</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1013; 8457</t>
+          <t>985; 8044</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2005</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6200</t>
+          <t>0; 6213</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6149</t>
+          <t>0; 6271</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6957; 19201</t>
+          <t>7090; 19893</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6679; 20830</t>
+          <t>6539; 19941</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2479; 11472</t>
+          <t>1994; 10904</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24028; 43656</t>
+          <t>24735; 44450</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16889; 35937</t>
+          <t>17917; 36622</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10682; 25800</t>
+          <t>10319; 25973</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6362</t>
+          <t>0; 7089</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 8315</t>
+          <t>948; 8898</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7345</t>
+          <t>0; 6499</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25356; 46594</t>
+          <t>25324; 45947</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19834; 39872</t>
+          <t>19638; 39862</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12275; 28163</t>
+          <t>12399; 27859</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4932; 16054</t>
+          <t>4622; 15794</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14311; 30363</t>
+          <t>14238; 29662</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6412; 17885</t>
+          <t>6472; 17446</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5813</t>
+          <t>0; 5640</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>912; 7620</t>
+          <t>876; 7229</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5273</t>
+          <t>0; 4910</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6138; 18371</t>
+          <t>6460; 18096</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16211; 34215</t>
+          <t>16715; 33003</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7080; 18768</t>
+          <t>7445; 19355</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11947; 26015</t>
+          <t>11701; 25409</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4127; 15976</t>
+          <t>4041; 15783</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5109; 16539</t>
+          <t>5135; 16201</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4861</t>
+          <t>0; 5426</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4994</t>
+          <t>0; 5696</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4619</t>
+          <t>0; 4982</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12016; 27407</t>
+          <t>12325; 27436</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4244; 18117</t>
+          <t>4275; 16516</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5725; 18319</t>
+          <t>5608; 17579</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3342; 12302</t>
+          <t>3204; 12272</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1009; 11843</t>
+          <t>1007; 12052</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>823; 9162</t>
+          <t>839; 10068</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 6783</t>
+          <t>0; 7360</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>949; 8055</t>
+          <t>932; 7445</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5986</t>
+          <t>0; 5880</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4304; 15525</t>
+          <t>4408; 15327</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3132; 15707</t>
+          <t>3112; 15455</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1951; 11407</t>
+          <t>1746; 11093</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9099; 21486</t>
+          <t>9989; 21931</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11211; 26184</t>
+          <t>10726; 25932</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3641; 13565</t>
+          <t>3494; 13243</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1032; 7539</t>
+          <t>1017; 7622</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5840</t>
+          <t>0; 4824</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1770</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11962; 27070</t>
+          <t>12208; 26474</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11403; 26789</t>
+          <t>12239; 27453</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3352; 12969</t>
+          <t>3473; 13537</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>15380; 31107</t>
+          <t>15349; 31378</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>31440; 53739</t>
+          <t>30580; 54682</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35825; 59273</t>
+          <t>37349; 60386</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 7777</t>
+          <t>0; 8551</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6653; 20832</t>
+          <t>7220; 21222</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10379; 25495</t>
+          <t>9986; 24119</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16771; 35546</t>
+          <t>17964; 34799</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>41911; 69247</t>
+          <t>41921; 69328</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>51379; 79920</t>
+          <t>51940; 79561</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>40769; 64096</t>
+          <t>41174; 62538</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>21864; 44641</t>
+          <t>21867; 44059</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9623; 23841</t>
+          <t>9708; 24075</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4118; 15757</t>
+          <t>4042; 15268</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4095; 15299</t>
+          <t>4190; 15880</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2171; 11668</t>
+          <t>2184; 11671</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>48684; 73977</t>
+          <t>47637; 73899</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>29254; 53693</t>
+          <t>29101; 52655</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>13196; 31130</t>
+          <t>13551; 31997</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>146547; 191499</t>
+          <t>148595; 191333</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>137926; 184183</t>
+          <t>138297; 185369</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>97643; 138260</t>
+          <t>98347; 139481</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13395; 33379</t>
+          <t>12894; 30914</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>24372; 47132</t>
+          <t>24164; 47385</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21270; 41895</t>
+          <t>20725; 41942</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>166235; 214789</t>
+          <t>166517; 214680</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>167872; 222191</t>
+          <t>169939; 222787</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>125999; 173037</t>
+          <t>126555; 170583</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$medico-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25A$medico-Provincia-trans_dic.xlsx
@@ -678,17 +678,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,6; 40,47</t>
+          <t>15,57; 42,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,48; 21,49</t>
+          <t>6,3; 20,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 10,19</t>
+          <t>1,26; 11,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,27 +698,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,52</t>
+          <t>0,0; 15,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,06</t>
+          <t>0,0; 13,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,66; 29,9</t>
+          <t>11,01; 30,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,4; 16,46</t>
+          <t>5,73; 16,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,33</t>
+          <t>1,57; 8,5</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,73; 39,04</t>
+          <t>21,26; 38,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,81; 30,28</t>
+          <t>14,7; 30,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,27; 35,91</t>
+          <t>14,29; 35,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,42</t>
+          <t>0,0; 23,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 14,88</t>
+          <t>1,64; 16,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,19</t>
+          <t>0,0; 21,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,13; 32,89</t>
+          <t>18,43; 33,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,86; 22,05</t>
+          <t>11,36; 22,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,2; 27,41</t>
+          <t>12,13; 28,58</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 24,78</t>
+          <t>7,35; 24,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,3; 36,04</t>
+          <t>16,26; 35,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,44; 28,14</t>
+          <t>10,6; 28,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,62</t>
+          <t>0,0; 40,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 22,05</t>
+          <t>2,79; 22,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,79</t>
+          <t>0,0; 14,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,29; 23,21</t>
+          <t>8,13; 23,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,52; 28,68</t>
+          <t>14,01; 29,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,31; 21,6</t>
+          <t>7,46; 21,27</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,42; 33,49</t>
+          <t>13,84; 33,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 14,97</t>
+          <t>3,92; 15,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 18,6</t>
+          <t>5,28; 17,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,4</t>
+          <t>0,0; 11,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,25</t>
+          <t>0,0; 13,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,15</t>
+          <t>0,0; 12,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,85; 24,16</t>
+          <t>10,48; 24,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 10,87</t>
+          <t>3,41; 12,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 13,34</t>
+          <t>4,21; 13,29</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,79; 29,85</t>
+          <t>8,36; 30,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 23,9</t>
+          <t>2,02; 25,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,64; 31,73</t>
+          <t>2,55; 30,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,36</t>
+          <t>0,0; 22,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 27,73</t>
+          <t>3,29; 27,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,42</t>
+          <t>0,0; 33,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,29; 21,85</t>
+          <t>6,94; 23,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,03; 20,0</t>
+          <t>4,12; 20,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,58; 22,73</t>
+          <t>3,76; 22,22</t>
         </is>
       </c>
     </row>
@@ -1228,27 +1228,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,89; 41,48</t>
+          <t>17,38; 42,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,91; 31,2</t>
+          <t>12,59; 30,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,87; 29,84</t>
+          <t>7,89; 28,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,41; 40,52</t>
+          <t>5,42; 40,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,08</t>
+          <t>0,0; 23,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1258,17 +1258,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,03; 36,93</t>
+          <t>17,95; 35,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,66; 26,16</t>
+          <t>10,71; 26,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,68; 22,13</t>
+          <t>5,88; 22,78</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,65; 34,05</t>
+          <t>16,63; 34,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,82; 33,64</t>
+          <t>18,82; 32,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,43; 47,58</t>
+          <t>28,61; 46,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,02</t>
+          <t>0,0; 24,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,86; 23,11</t>
+          <t>7,61; 22,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,83; 28,56</t>
+          <t>12,27; 29,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,37; 27,83</t>
+          <t>14,14; 27,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,48; 27,26</t>
+          <t>16,23; 26,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>24,58; 37,65</t>
+          <t>24,47; 37,72</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>29,73; 45,15</t>
+          <t>29,74; 46,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,79; 33,83</t>
+          <t>16,97; 34,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,51; 23,58</t>
+          <t>9,55; 25,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,6; 21,15</t>
+          <t>4,67; 20,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,26; 23,73</t>
+          <t>5,86; 21,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,42; 18,25</t>
+          <t>3,39; 17,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,61; 35,07</t>
+          <t>22,91; 35,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,76; 26,71</t>
+          <t>14,79; 27,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,16; 19,27</t>
+          <t>7,84; 19,46</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>23,79; 30,63</t>
+          <t>23,81; 30,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,95; 22,71</t>
+          <t>16,94; 22,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16,24; 23,04</t>
+          <t>16,32; 22,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,14; 12,33</t>
+          <t>5,37; 12,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,26</t>
+          <t>6,2; 12,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,17; 12,49</t>
+          <t>6,25; 12,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,02; 24,53</t>
+          <t>19,03; 24,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,13; 18,52</t>
+          <t>14,09; 18,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,44; 18,12</t>
+          <t>13,34; 18,32</t>
         </is>
       </c>
     </row>
@@ -1861,17 +1861,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7247; 18796</t>
+          <t>7232; 19821</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5252; 17432</t>
+          <t>5113; 16939</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>985; 8044</t>
+          <t>997; 8823</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1881,27 +1881,27 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6213</t>
+          <t>0; 6399</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6271</t>
+          <t>0; 7078</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7090; 19893</t>
+          <t>7326; 19974</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6539; 19941</t>
+          <t>6942; 20242</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1994; 10904</t>
+          <t>2056; 11131</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24735; 44450</t>
+          <t>24207; 44263</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17917; 36622</t>
+          <t>17773; 36611</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10319; 25973</t>
+          <t>10332; 25601</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7089</t>
+          <t>0; 6035</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>948; 8898</t>
+          <t>982; 9597</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6499</t>
+          <t>0; 6418</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25324; 45947</t>
+          <t>25749; 46519</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19638; 39862</t>
+          <t>20536; 40189</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12399; 27859</t>
+          <t>12330; 29038</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4622; 15794</t>
+          <t>4685; 15686</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14238; 29662</t>
+          <t>13386; 29295</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6472; 17446</t>
+          <t>6572; 17935</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5640</t>
+          <t>0; 5827</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>876; 7229</t>
+          <t>915; 7485</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4910</t>
+          <t>0; 4070</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6460; 18096</t>
+          <t>6341; 18466</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16715; 33003</t>
+          <t>16117; 34390</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7445; 19355</t>
+          <t>6688; 19064</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11701; 25409</t>
+          <t>10504; 25084</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4041; 15783</t>
+          <t>4137; 16627</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5135; 16201</t>
+          <t>4595; 15240</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5426</t>
+          <t>0; 4304</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5696</t>
+          <t>0; 6083</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4982</t>
+          <t>0; 5540</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12325; 27436</t>
+          <t>11900; 27592</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4275; 16516</t>
+          <t>5175; 18281</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5608; 17579</t>
+          <t>5549; 17510</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3204; 12272</t>
+          <t>3437; 12567</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1007; 12052</t>
+          <t>1018; 13008</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>839; 10068</t>
+          <t>808; 9676</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 7360</t>
+          <t>0; 6402</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>932; 7445</t>
+          <t>882; 7487</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5880</t>
+          <t>0; 5642</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4408; 15327</t>
+          <t>4869; 16266</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3112; 15455</t>
+          <t>3181; 16023</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1746; 11093</t>
+          <t>1833; 10844</t>
         </is>
       </c>
     </row>
@@ -2676,27 +2676,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9989; 21931</t>
+          <t>9189; 22343</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10726; 25932</t>
+          <t>10465; 25231</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3494; 13243</t>
+          <t>3499; 12832</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1017; 7622</t>
+          <t>1020; 7542</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4824</t>
+          <t>0; 5136</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2706,17 +2706,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12208; 26474</t>
+          <t>12868; 25724</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12239; 27453</t>
+          <t>11237; 27854</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3473; 13537</t>
+          <t>3595; 13933</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>15349; 31378</t>
+          <t>15329; 31383</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>30580; 54682</t>
+          <t>30596; 53218</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37349; 60386</t>
+          <t>36310; 59597</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 8551</t>
+          <t>0; 8002</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7220; 21222</t>
+          <t>6984; 21034</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9986; 24119</t>
+          <t>10356; 24516</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17964; 34799</t>
+          <t>17680; 34876</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>41921; 69328</t>
+          <t>41273; 68313</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>51940; 79561</t>
+          <t>51707; 79723</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>41174; 62538</t>
+          <t>41195; 63809</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>21867; 44059</t>
+          <t>22094; 44675</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9708; 24075</t>
+          <t>9751; 25551</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4042; 15268</t>
+          <t>3369; 15108</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4190; 15880</t>
+          <t>3920; 14491</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2184; 11671</t>
+          <t>2168; 11277</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>47637; 73899</t>
+          <t>48263; 74621</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>29101; 52655</t>
+          <t>29157; 53823</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>13551; 31997</t>
+          <t>13025; 32309</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>148595; 191333</t>
+          <t>148718; 190845</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>138297; 185369</t>
+          <t>138274; 185072</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>98347; 139481</t>
+          <t>98799; 136657</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12894; 30914</t>
+          <t>13457; 31506</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>24164; 47385</t>
+          <t>23978; 46866</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20725; 41942</t>
+          <t>20976; 41737</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>166517; 214680</t>
+          <t>166531; 214916</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>169939; 222787</t>
+          <t>169436; 221388</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>126555; 170583</t>
+          <t>125552; 172434</t>
         </is>
       </c>
     </row>
